--- a/docs/_baseline/water_bulk.xlsx
+++ b/docs/_baseline/water_bulk.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130">
   <si>
     <t>※ 엑셀 기반 수질/생태계 데이터 베이스 작성/관리 시 주의 사항</t>
   </si>
@@ -404,9 +404,6 @@
   </si>
   <si>
     <t>곡교천</t>
-  </si>
-  <si>
-    <t>평지형</t>
   </si>
   <si>
     <t>맑음</t>
@@ -4295,7 +4292,7 @@
         <v>119</v>
       </c>
       <c r="F8" s="89" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="G8" s="89"/>
       <c r="H8" s="89"/>
@@ -5390,7 +5387,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="89" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G11" s="89"/>
       <c r="H11" s="89"/>
@@ -5755,7 +5752,7 @@
         <v>120</v>
       </c>
       <c r="F12" s="89" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G12" s="89"/>
       <c r="H12" s="89"/>
@@ -6120,7 +6117,7 @@
         <v>121</v>
       </c>
       <c r="F13" s="89" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G13" s="89"/>
       <c r="H13" s="89"/>
